--- a/光伏配储项目/电价数据/2026/吉康站.xlsx
+++ b/光伏配储项目/电价数据/2026/吉康站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.59057</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.79455</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.66503</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.60805</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.58063</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.5799299999999999</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.45065</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.46963</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43987</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.43504</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.43209</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.42025</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.40616</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40611</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.39323</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.41157</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.43734</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.42435</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.40068</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.39326</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.42723</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.40073</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.43136</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.42404</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.43449</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.4211</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.51762</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.40795</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31129</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37643</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32223</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.38593</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.20018</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.2216</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.26553</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.21616</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.17727</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.20183</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.2872</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.25071</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.29909</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.06227000000000001</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.15983</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.24326</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.24118</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.24593</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.23045</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.21722</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.91122</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.22417</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.52262</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.53835</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.28781</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.29805</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.31159</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.51654</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.59665</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.58512</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.72665</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.18597</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39363</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.59956</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.42987</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43505</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6549700000000001</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.9096900000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.51552</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.25026</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.35316</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.11897</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.19832</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.32556</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.46963</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.48875</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.72946</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.7809199999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.28588</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.10035</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.86676</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.7938</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.75375</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51435</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47694</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46452</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.4145</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42396</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7013200000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.74932</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.86412</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.90522</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.48991</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5078199999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.4975</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.4803</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39691</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46286</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37625</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.35266</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.35782</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.34323</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.34234</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.35281</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.38477</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.7093400000000001</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.55911</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.66784</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43428</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.4087</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37639</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38907</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42917</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.51005</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35603</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29867</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.34261</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.39085</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.41828</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.58278</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.8577899999999999</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.07516</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.5838</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.93576</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.89005</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.56024</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.84296</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.2525</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.05685</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.35356</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.41026</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.50358</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.5884400000000001</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.54691</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.53825</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.85819</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.6054400000000001</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.76373</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.81656</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.19536</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.65304</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.15751</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.86666</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.24479</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.14894</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.30797</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.08881</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.13362</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.69257</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.02493</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.8951699999999999</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.03074</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.92902</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.05656</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.86382</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.44735</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.81512</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.83608</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44675</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42626</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44131</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33273</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37432</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35379</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33436</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50317</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.4833</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48078</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44188</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41101</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36591</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38741</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36168</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42437</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.43929</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33503</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39309</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36507</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36607</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35221</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37902</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39193</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.46787</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44167</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43465</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39226</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.20419</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.24221</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27862</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.35394</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.15939</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.55059</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.49595</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.49045</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.5800599999999999</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.5872200000000001</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.66827</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.63436</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.88918</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.59021</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.7021900000000001</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.77815</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.8678899999999999</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.52262</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.5252100000000001</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.7789700000000001</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.72956</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.6458700000000001</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.6384099999999999</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.5011100000000001</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.59005</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.41303</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38775</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.46213</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.50376</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.51129</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.5778099999999999</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.61187</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.58065</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.6016699999999999</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.23899</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.61112</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.70984</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46845</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50948</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5768</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.7047100000000001</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.69885</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.8205800000000001</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.43401</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.5822000000000001</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.45007</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.5310199999999999</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.60278</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.71985</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.5634</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.85125</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.68972</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.57921</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.5153099999999999</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.6473300000000001</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.43808</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45456</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39616</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36195</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34803</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34165</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.51393</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49192</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.43885</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38839</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38809</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.38685</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36626</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35823</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38691</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38497</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36131</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.4455</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36273</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35701</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35818</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33173</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38689</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34885</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39287</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41589</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.4388</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35714</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.44804</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.37844</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.33358</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.44873</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.36333</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.62891</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.51515</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.4764</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.38721</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.27656</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.8582799999999999</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.38049</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.40785</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.59487</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.49232</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.4203</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39702</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.38522</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.37326</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.48655</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.6110399999999999</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.41255</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.48489</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45056</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.45682</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39854</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47115</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.5354</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.64188</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.49576</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.67332</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.53569</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.5039100000000001</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5021100000000001</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.46415</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.4412</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.4225</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41304</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.36637</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.38154</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34583</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32267</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31302</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31071</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.41088</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.3805</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38272</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31353</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30951</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31332</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32289</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34617</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30279</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.29244</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.2446</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.29024</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.26579</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14491</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.29852</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.02668</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.27271</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.28243</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.24811</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.21572</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.21318</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.19093</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.39067</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.38604</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.24678</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.24214</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.22337</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.08618000000000001</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.17841</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.14831</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.01429</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26347</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30061</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30482</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32966</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.36314</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.35608</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35218</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.36688</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.38202</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.44775</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.37767</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.45457</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.32984</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.44731</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.33762</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.31762</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.29734</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.31439</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.24429</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.28348</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.21114</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.28873</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.09182</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.2212</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.27881</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.25989</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.24118</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.27484</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.22956</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.28268</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.30029</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.25403</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.2854100000000001</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.1033</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04389</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04482</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01117</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.2084</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05036</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27865</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19341</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.19751</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.01471</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06254999999999999</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.06075999999999999</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.32312</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.30323</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.37621</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29729</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.39403</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.3786</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42616</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45297</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41527</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38147</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29428</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88749</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8704700000000001</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.66416</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33084</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5764</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77754</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39988</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6218400000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.4489</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41938</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.33697</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39545</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3578</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.39767</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.41149</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38034</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44631</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.37726</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.50176</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.36385</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5603400000000001</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6511699999999999</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8708400000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46185</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.49248</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.39889</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.69526</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.83539</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.36477</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.48707</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32409</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29704</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.27888</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.5011100000000001</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.5788099999999999</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.4457</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31554</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.29632</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29714</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.2959</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30943</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.30182</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.23017</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.28024</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.28187</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.2846</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.29733</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.31005</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.32151</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.30895</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.33473</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9037999999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.36085</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.33359</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.32297</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.31298</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.31182</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.38262</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.32372</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.31455</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.32122</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.32302</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.28835</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.30009</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.30975</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.31183</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30777</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30698</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28244</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30807</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.23914</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.3042</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.40599</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31726</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27374</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19499</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.29927</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29886</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31529</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27609</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30386</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.30437</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.29568</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.2811</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.28956</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.24313</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.2937</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.2664</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.28374</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.2813</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.28174</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.29146</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28503</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.3141600000000001</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.24927</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.29289</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.30862</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.30961</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.2696</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.30708</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.30302</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.30592</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.2844</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.34755</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.31565</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.41335</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.41887</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.30391</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.40245</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.26066</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.81489</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.38922</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.09152</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.65659</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7457</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.60963</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.34892</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.2969</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.41698</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.46598</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.40894</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.37092</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.38595</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.36355</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.38276</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.3867</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.40568</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.40745</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.34893</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.39976</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.3868</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.39456</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3728399999999999</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.46848</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.22762</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.26908</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.29769</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.2948</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.31766</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.29761</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.28642</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.28937</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.46618</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.05539</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24524</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.29542</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.14532</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.26331</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27349</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.02943</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.32559</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.25585</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.2474</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30247</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.27901</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.27043</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.28325</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.29258</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.30436</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.30789</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.2971</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.3013</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.30348</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.30765</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.33613</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.31766</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.29187</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.34215</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.30754</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.32502</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.37089</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.6664500000000001</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.37023</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.36122</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.39574</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.30274</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.27336</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.28092</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.27882</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.22185</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.31603</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.23434</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.23998</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.22993</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.23657</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.21208</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.25592</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.27526</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.27328</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.29519</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.29131</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.20498</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.2054</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.28173</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.29627</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.28684</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.09023</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.22471</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.26347</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.09114</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.24929</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.26269</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.24813</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.29215</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.31399</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.27381</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.29024</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.2198</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.29831</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.15469</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.30058</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.20225</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.22213</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.2701</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.2652</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23689</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.23275</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.23131</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28793</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.23661</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.21749</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.21839</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.26683</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.23099</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.27139</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.23308</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26462</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.27795</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.25018</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.21373</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.22663</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.22816</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.21977</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.25785</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.23372</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.27573</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.30967</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.30188</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.32361</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.30779</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.3405899999999999</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.33329</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.35356</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.42579</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.36782</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.37659</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.37064</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.28582</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.30641</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.30791</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.37024</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.36934</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.32874</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.31418</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35694</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.32248</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.31571</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.30941</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3159</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.31628</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.34202</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28806</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.30267</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30634</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28919</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.29219</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.28259</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.27177</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27803</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30127</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31349</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29927</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.30356</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23456</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30242</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.29432</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.30977</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31245</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.30892</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.35404</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32117</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.3648</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.42334</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.34292</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.39998</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.39596</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.40476</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.47359</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.36176</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.3728</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.33663</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.40412</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.35422</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.32224</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.33604</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.32568</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.3744</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.38964</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.31769</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.31529</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.31468</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.31253</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.30991</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.31346</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36131</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33611</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.42735</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.20533</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.44583</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.72739</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.42245</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.52826</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.5079900000000001</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.41032</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.47638</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.5502400000000001</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.42562</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.46943</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.41469</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.62186</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27937</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.46495</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.37216</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.38242</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.40768</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.7897999999999999</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.5177999999999999</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.42752</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.48883</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.46275</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.44949</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.61278</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.46477</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.47711</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.49968</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.4431</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.50458</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.38109</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.42106</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.38393</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.36876</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.6620499999999999</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.49351</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.47399</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.4689700000000001</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.45073</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.72833</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.40211</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.45932</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.46657</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.41277</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.49041</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22453</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.34759</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.28262</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30958</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.12254</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.24792</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.33813</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.39669</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.29885</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.3054</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.31312</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.25276</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.24308</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.29715</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.30145</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.29462</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.29353</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.24541</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.30645</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.2421</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.21747</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.26679</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.30106</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.30424</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.28593</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.24183</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.24713</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.25876</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.25705</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.2347</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.22353</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.26321</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.27041</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.31489</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.3751</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32828</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.31264</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29275</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.31202</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.31163</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29699</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.30677</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.26405</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.30572</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.30601</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.29655</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.30565</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.30773</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.31469</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.31041</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.29887</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.29776</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.28185</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.29406</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.28381</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.38735</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.36812</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.31076</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33816</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.30712</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.33901</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.30688</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.35215</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.29594</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.33503</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.26075</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.23027</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.27688</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.33069</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.33153</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.33248</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.30612</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.32737</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.12255</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.30912</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.29707</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.30554</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.30341</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.30794</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.30427</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.29763</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.30327</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.31148</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.30246</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.29413</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.30787</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.29534</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.30385</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.28458</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30749</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31728</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31283</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.31246</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32626</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.37721</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.33708</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.32983</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.36548</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.42336</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.35692</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.63935</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.75275</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.38174</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.25961</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.39969</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.37352</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.31437</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.39224</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.34314</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.33722</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.32872</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.34697</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.33228</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.33901</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.42862</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.31211</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.29128</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.31251</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.28688</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.30914</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.28445</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.30186</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.30489</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31221</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.3117200000000001</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.34599</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.35268</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.34837</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.36499</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.4422</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.37942</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.41358</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.37418</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.37846</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32373</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.3958</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43929</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.53242</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.5189</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6782100000000001</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.63576</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.69014</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.41314</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.83413</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.42331</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.62686</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.49842</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.52178</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.43277</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.4813</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.40446</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.39783</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.35435</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.33111</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34571</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.38877</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.4304</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.39785</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.47631</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.36061</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.3691</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.33361</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.35328</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.39353</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.36303</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.37899</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.4663</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.43764</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.44241</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.4851</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.52193</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.57308</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.6011599999999999</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.41559</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.36939</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.38259</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.42273</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.40034</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.42859</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.67736</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.41454</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.84853</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.40089</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.44596</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.36604</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.3784</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.38693</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33326</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.32541</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.36526</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.38851</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.3623</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.39184</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.39038</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.40754</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.4614</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.5096000000000001</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.5974400000000001</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.44356</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.5178200000000001</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.48628</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.42782</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.52712</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.75405</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6063</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.65355</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.41336</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.39816</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.37853</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.37282</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.35732</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.41118</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.36073</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.36568</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.36908</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.41554</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.4054700000000001</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.36369</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.3972</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.34478</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.33604</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.33302</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.34265</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.13733</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.31091</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.31197</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.32252</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.34246</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.38731</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.38047</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.36773</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.45018</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.38869</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.36161</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.37582</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.82233</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.39528</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.38449</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.44266</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.39652</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45359</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.4331</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.45491</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.4151</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.24172</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.27609</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.30458</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.31213</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.35553</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.27066</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.40847</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39855</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.37576</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38917</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.27806</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.27769</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.29753</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.32047</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.28799</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.27619</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.31765</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.32771</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.25231</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.23334</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.26309</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.25265</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.26393</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.23843</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.3777799999999999</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.35751</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.28942</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.27783</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.23442</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.13724</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.29579</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.12806</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.12712</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.23451</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.1213</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.25384</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.23344</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.12101</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.22083</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.22688</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.24906</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.22368</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.22723</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.23079</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.11713</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.23434</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.11662</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.10076</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.24859</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.23192</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.21098</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.09221</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.27126</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.27712</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.11064</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.27422</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.2782</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.24761</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.28909</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.28227</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.01134</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.30055</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30563</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.18933</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.27171</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.01629</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28459</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.2867</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.24827</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.27829</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31239</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30441</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.28239</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.29196</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.25041</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.2539</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27623</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28476</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.25502</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.30565</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.30125</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.29699</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.31589</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.29349</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.28348</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.28788</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.29819</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.30405</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.30634</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.29134</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.27654</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.29194</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.26778</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.29255</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.29836</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.2873</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.29242</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.2445</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.25372</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.28859</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.22971</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.30142</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.22884</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.27079</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.2628</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.30144</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.30055</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.30463</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.29735</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.14867</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.23552</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.23187</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.28539</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.10539</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.24175</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.25639</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.25011</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.13394</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.09895999999999999</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.1076</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.10758</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.10584</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.10584</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.10689</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.23683</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.09697</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.10584</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.10601</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.22553</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.09903000000000001</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.09893</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.11032</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.07092</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.25528</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.11401</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.00208</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00022</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14264</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02186</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01588</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04086</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04826</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02933</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04531</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00066</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27489</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04931</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03828</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.0215</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03629</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.2003</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26477</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28764</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27804</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.29058</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.29771</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.10876</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.29747</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.32174</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.29507</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30436</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.36455</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.29927</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.52604</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.47272</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.20722</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.24333</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.23299</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.23879</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.23534</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.11408</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.23014</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.21545</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.11872</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.07856</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.09547</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.10608</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.11998</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.08516</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.13159</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.13825</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.1504</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.42548</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.27107</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.30716</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.33489</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.1056</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.29875</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.27272</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.5592</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.86773</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.85938</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.37089</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.10611</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.09720999999999999</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.27196</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.31112</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.27471</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.16846</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.14141</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.28274</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.28435</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00114</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.28489</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00066</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.30513</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06634000000000001</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.29937</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30173</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30061</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25456</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.2919</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47348</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.34777</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.08238</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.65859</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.5549299999999999</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.59475</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.0714</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.9717100000000001</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.56408</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.72296</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.61072</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.82951</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.82774</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.832</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.92962</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.5529500000000001</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.6067400000000001</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.56063</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.35215</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.33382</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.39581</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.46638</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.24768</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.43674</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.48183</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.37894</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.36823</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.26845</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.29356</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.2929</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.28431</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.26394</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.25795</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.23681</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.2526</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.22959</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.23301</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.11253</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.24463</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.2562</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.38175</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.37103</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.29963</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.2859</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.30196</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.36165</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.36704</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.39907</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.34305</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30886</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30792</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25778</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30177</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30144</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32666</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31457</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.32359</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.39295</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.37374</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.40576</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.39387</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.54422</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.47897</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.40307</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.37713</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.3732</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36129</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.41305</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.31915</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.39837</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.39732</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.38593</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.36729</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.35832</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.34337</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.34329</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33357</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.36506</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.34588</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.46581</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.69628</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.44491</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.46414</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.46718</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.39338</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.37513</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.34154</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29939</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.33283</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.3433</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33642</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33851</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.4962</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.43085</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47233</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.54791</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.8351799999999999</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.9288200000000001</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.45599</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.50991</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.5599299999999999</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.85499</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.8687999999999999</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.49438</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.63654</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.47852</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.41256</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.40899</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.44358</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.3995</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41854</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.35414</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.36888</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.34461</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.38657</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.34442</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.36106</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.22119</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.33795</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.43221</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.36415</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.35676</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.34777</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.33427</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.33966</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.33309</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.33401</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31202</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.31569</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.33657</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39106</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.35709</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35374</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.4347200000000001</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37976</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36361</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.39295</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35127</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.3416</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34418</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.3642</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.38157</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.36651</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.38576</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36641</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.4104</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.40072</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.50238</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.56616</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.07413</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.88954</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.63905</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.7853600000000001</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.50046</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.6038</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.57237</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.45363</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.7553200000000001</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.71431</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.9656</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.86975</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.77815</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.71075</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39483</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44999</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.34242</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.29392</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.33299</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33227</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32151</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.31501</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.31942</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33525</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.12256</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.31571</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36781</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.36822</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.3459100000000001</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.34219</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33197</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.38729</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.39551</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32966</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.28503</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.44728</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.36487</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.61858</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.39198</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.36645</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.20108</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.42063</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.30409</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43245</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.5961900000000001</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.37846</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.35717</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35324</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.44058</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.41247</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.35757</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.3654</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.38788</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.48206</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.36086</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.40151</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.59537</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.43067</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.47459</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.42673</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.46497</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.5771499999999999</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.41174</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.4619</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.41971</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.45443</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.38636</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37483</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.38509</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.34815</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34283</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.8778899999999999</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.4422</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.51974</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.47947</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.46281</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.35621</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.41229</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.36315</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.36607</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.35866</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35383</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.35275</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.36136</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.36766</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.39793</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.31458</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.39091</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.32628</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.32161</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.43403</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.48866</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.31159</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.36333</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.37391</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.39659</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.37581</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.37581</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.36494</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39923</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.38608</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.37802</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.3752</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37251</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.37658</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.45989</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.52843</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.44336</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.3855</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.45247</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.43251</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.42594</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35791</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.35017</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.40005</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.37785</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.3719</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36899</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.35695</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.35348</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.35757</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.35208</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.34683</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.3416</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31392</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17591</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30508</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29529</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14558</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.1984</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14352</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28838</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04604</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12051</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22431</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26011</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14622</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14393</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28385</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.19066</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22658</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26108</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15217</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30839</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.15518</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30094</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.30401</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19625</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14113</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.27848</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.27215</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.28867</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.35224</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.36367</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.3828</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.46218</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.41374</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.36452</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.48635</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.36698</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37617</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36664</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.36871</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.37238</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.45349</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39167</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39755</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.37984</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38892</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39162</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37236</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.37579</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37786</v>
       </c>
     </row>
   </sheetData>
